--- a/data/trans_dic/P16A_n_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,89; 21,52</t>
+          <t>13,01; 22,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,97; 30,02</t>
+          <t>19,58; 30,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,5; 24,08</t>
+          <t>14,1; 23,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,58; 32,14</t>
+          <t>21,37; 32,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,5; 32,81</t>
+          <t>21,34; 32,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,14; 47,8</t>
+          <t>35,69; 48,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,09; 36,49</t>
+          <t>25,61; 36,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,98; 42,29</t>
+          <t>33,05; 42,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,34; 25,76</t>
+          <t>18,36; 25,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,73; 37,04</t>
+          <t>29,24; 37,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,51; 28,94</t>
+          <t>21,34; 28,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,21; 35,37</t>
+          <t>28,29; 35,32</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,92; 17,11</t>
+          <t>11,07; 17,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,09; 30,65</t>
+          <t>22,24; 30,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,32; 27,05</t>
+          <t>19,56; 27,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,41; 29,88</t>
+          <t>20,93; 30,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,83; 34,94</t>
+          <t>26,78; 34,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,51; 45,82</t>
+          <t>37,32; 46,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,57; 42,0</t>
+          <t>33,39; 41,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,64; 42,31</t>
+          <t>34,72; 42,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,96; 25,15</t>
+          <t>19,88; 25,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,77; 37,18</t>
+          <t>30,9; 37,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,28; 32,94</t>
+          <t>27,43; 33,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,93; 35,11</t>
+          <t>29,17; 34,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 20,4</t>
+          <t>12,55; 20,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,65; 35,03</t>
+          <t>24,59; 35,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,41; 26,34</t>
+          <t>17,53; 26,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,51; 39,87</t>
+          <t>30,06; 40,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,6; 31,02</t>
+          <t>21,98; 31,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,11; 49,26</t>
+          <t>38,53; 49,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,72; 33,85</t>
+          <t>24,05; 34,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,82; 47,49</t>
+          <t>39,38; 47,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,44; 24,91</t>
+          <t>18,14; 24,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33,21; 40,61</t>
+          <t>33,28; 41,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,34; 28,7</t>
+          <t>22,41; 29,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35,9; 42,85</t>
+          <t>35,78; 42,35</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,11; 22,06</t>
+          <t>14,63; 22,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,3; 29,79</t>
+          <t>19,99; 29,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,34; 35,01</t>
+          <t>24,98; 35,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,31; 41,14</t>
+          <t>28,67; 41,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,76; 36,91</t>
+          <t>27,56; 37,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,46; 50,8</t>
+          <t>40,33; 50,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,88; 49,7</t>
+          <t>38,79; 49,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,18; 46,14</t>
+          <t>22,06; 46,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,94; 27,96</t>
+          <t>21,98; 28,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31,59; 39,04</t>
+          <t>31,91; 38,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,58; 40,74</t>
+          <t>33,52; 41,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,3; 41,43</t>
+          <t>26,05; 41,3</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,32; 21,64</t>
+          <t>10,82; 21,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,77; 34,51</t>
+          <t>21,86; 34,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,66; 25,33</t>
+          <t>14,37; 25,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,97; 36,14</t>
+          <t>24,58; 35,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,28; 43,22</t>
+          <t>28,56; 42,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,52; 59,85</t>
+          <t>47,25; 60,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,93; 50,52</t>
+          <t>38,28; 51,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,2; 46,26</t>
+          <t>19,35; 46,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,76; 31,04</t>
+          <t>21,34; 29,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36,19; 45,8</t>
+          <t>36,2; 45,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28,22; 36,61</t>
+          <t>27,95; 36,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,06; 38,97</t>
+          <t>23,97; 39,27</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,93; 22,56</t>
+          <t>13,99; 22,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,78; 37,73</t>
+          <t>26,95; 38,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,98; 25,68</t>
+          <t>15,71; 26,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32,43; 43,03</t>
+          <t>32,82; 42,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,64; 35,63</t>
+          <t>24,13; 34,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,3; 49,98</t>
+          <t>38,01; 50,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,8; 36,91</t>
+          <t>25,48; 36,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39,81; 49,56</t>
+          <t>39,84; 49,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,49; 27,44</t>
+          <t>20,44; 27,38</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33,78; 42,38</t>
+          <t>34,32; 42,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,15; 29,91</t>
+          <t>22,24; 29,93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37,32; 44,21</t>
+          <t>37,39; 44,35</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,59; 20,79</t>
+          <t>14,52; 20,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,03; 27,96</t>
+          <t>20,45; 27,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,97; 24,82</t>
+          <t>17,82; 24,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,37; 39,33</t>
+          <t>30,53; 39,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,88; 32,52</t>
+          <t>24,95; 31,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,26; 41,95</t>
+          <t>34,36; 41,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,49; 33,56</t>
+          <t>26,79; 33,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43,29; 77,27</t>
+          <t>43,27; 79,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,68; 25,47</t>
+          <t>20,77; 25,36</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28,67; 34,0</t>
+          <t>28,63; 33,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,52; 28,26</t>
+          <t>23,52; 28,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,79; 68,25</t>
+          <t>38,75; 66,31</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,98; 23,8</t>
+          <t>17,92; 23,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,5; 24,6</t>
+          <t>18,34; 24,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,65; 28,21</t>
+          <t>21,58; 27,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,82; 24,27</t>
+          <t>7,86; 24,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,07; 34,0</t>
+          <t>26,9; 33,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,93; 34,59</t>
+          <t>27,83; 34,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,62; 39,01</t>
+          <t>31,9; 38,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,35; 38,62</t>
+          <t>32,63; 38,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23,44; 27,88</t>
+          <t>23,52; 27,94</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24,23; 28,8</t>
+          <t>24,01; 28,68</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28,08; 32,75</t>
+          <t>27,72; 32,57</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,69; 30,17</t>
+          <t>15,09; 30,22</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,13; 18,69</t>
+          <t>16,14; 18,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23,8; 26,85</t>
+          <t>23,74; 26,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21,53; 24,43</t>
+          <t>21,45; 24,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22,24; 30,57</t>
+          <t>21,35; 30,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>28,15; 31,49</t>
+          <t>28,34; 31,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,38; 41,67</t>
+          <t>38,35; 41,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,07; 36,39</t>
+          <t>33,27; 36,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>38,68; 54,3</t>
+          <t>38,62; 53,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22,7; 24,77</t>
+          <t>22,67; 24,75</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31,64; 34,01</t>
+          <t>31,68; 33,94</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27,92; 30,15</t>
+          <t>27,81; 30,07</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>32,06; 41,87</t>
+          <t>32,31; 40,9</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35191; 58753</t>
+          <t>35510; 60669</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55904; 88471</t>
+          <t>57710; 88762</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42587; 70737</t>
+          <t>41414; 68530</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67208; 100104</t>
+          <t>66570; 100729</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>56068; 85573</t>
+          <t>55656; 84958</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>100937; 137295</t>
+          <t>102530; 138057</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72426; 105336</t>
+          <t>73947; 105579</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>95526; 122494</t>
+          <t>95732; 122731</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>97887; 137523</t>
+          <t>98029; 137170</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>167192; 215561</t>
+          <t>170189; 216288</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>125307; 168559</t>
+          <t>124322; 165007</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>169591; 212614</t>
+          <t>170043; 212276</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53837; 84359</t>
+          <t>54605; 86071</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>111687; 154952</t>
+          <t>112439; 153868</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97084; 135960</t>
+          <t>98304; 136170</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>110977; 154879</t>
+          <t>108500; 156441</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>135191; 176056</t>
+          <t>134970; 176320</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>196487; 239969</t>
+          <t>195487; 243780</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>175596; 219715</t>
+          <t>174659; 219201</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>178365; 217891</t>
+          <t>178811; 217264</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>198980; 250769</t>
+          <t>198194; 250393</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>316741; 382732</t>
+          <t>318099; 383251</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>279846; 337857</t>
+          <t>281382; 339341</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>298999; 362841</t>
+          <t>301473; 360958</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39340; 65060</t>
+          <t>40008; 65998</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>79888; 113510</t>
+          <t>79695; 113806</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55459; 83921</t>
+          <t>55848; 84064</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93251; 126000</t>
+          <t>95008; 126872</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>72449; 104038</t>
+          <t>73710; 105162</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>129977; 167998</t>
+          <t>131386; 168859</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79777; 113826</t>
+          <t>80889; 114700</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>135515; 165815</t>
+          <t>137495; 166903</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120633; 162969</t>
+          <t>118687; 160042</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>220855; 270115</t>
+          <t>221309; 273219</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>146325; 187939</t>
+          <t>146744; 190489</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>238773; 285019</t>
+          <t>238012; 281711</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>50624; 79115</t>
+          <t>52487; 81051</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75906; 111400</t>
+          <t>74759; 110778</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93764; 129518</t>
+          <t>92431; 130630</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88473; 128583</t>
+          <t>89624; 128718</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>103127; 137091</t>
+          <t>102388; 139040</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>157356; 197586</t>
+          <t>156856; 195268</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>150593; 192482</t>
+          <t>150219; 190666</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100755; 219506</t>
+          <t>104964; 222529</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>160206; 204179</t>
+          <t>160448; 205978</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>241005; 297842</t>
+          <t>243474; 297448</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>254250; 308515</t>
+          <t>253861; 312351</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>207342; 326607</t>
+          <t>205354; 325522</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>94188</t>
+          <t>94187</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23010; 43999</t>
+          <t>22002; 43111</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46279; 73383</t>
+          <t>46484; 73341</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30959; 53499</t>
+          <t>30342; 53746</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44631; 64596</t>
+          <t>43928; 63239</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>60806; 89762</t>
+          <t>59304; 87821</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>102153; 131423</t>
+          <t>103758; 133287</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82903; 110421</t>
+          <t>83667; 113156</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49688; 119712</t>
+          <t>50069; 119833</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>89444; 127549</t>
+          <t>87707; 123098</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>156400; 197955</t>
+          <t>156469; 196858</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>121302; 157356</t>
+          <t>120138; 158384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96539; 170509</t>
+          <t>104873; 171795</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37711; 61082</t>
+          <t>37873; 61517</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73380; 103360</t>
+          <t>73833; 105655</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42041; 67569</t>
+          <t>41345; 68746</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>87456; 116019</t>
+          <t>88482; 115150</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>68537; 99096</t>
+          <t>67112; 96389</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>104462; 139956</t>
+          <t>106444; 140625</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67735; 100800</t>
+          <t>69585; 98562</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>102344; 127401</t>
+          <t>102408; 128328</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>112461; 150644</t>
+          <t>112202; 150314</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>187162; 234816</t>
+          <t>190139; 234525</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>118788; 160372</t>
+          <t>119284; 160514</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>196564; 232849</t>
+          <t>196906; 233567</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>89735; 127842</t>
+          <t>89297; 125541</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>139410; 185343</t>
+          <t>135533; 183807</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>117996; 162959</t>
+          <t>117014; 160210</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>189580; 245546</t>
+          <t>190575; 245918</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>158760; 207556</t>
+          <t>159228; 204007</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>237724; 291103</t>
+          <t>238438; 287912</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>183120; 232030</t>
+          <t>185164; 232918</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>367636; 656232</t>
+          <t>367504; 673809</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>259116; 319157</t>
+          <t>260314; 317865</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>388981; 461223</t>
+          <t>388431; 459692</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>317074; 380895</t>
+          <t>317042; 381361</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>571654; 1005621</t>
+          <t>570939; 977098</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>133727; 177007</t>
+          <t>133282; 177286</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>144127; 191620</t>
+          <t>142913; 188713</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>168549; 219665</t>
+          <t>168003; 216469</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>72591; 225377</t>
+          <t>73019; 227205</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>212099; 266391</t>
+          <t>210750; 261217</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>230091; 284950</t>
+          <t>229313; 284878</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>261208; 322265</t>
+          <t>263548; 320524</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>232157; 277214</t>
+          <t>234211; 277385</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>357950; 425788</t>
+          <t>359280; 426686</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>388325; 461686</t>
+          <t>384904; 459734</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>450554; 525623</t>
+          <t>444815; 522716</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>258399; 496790</t>
+          <t>248424; 497521</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>528509; 612482</t>
+          <t>528764; 612259</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>815615; 920105</t>
+          <t>813379; 919139</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>730904; 829383</t>
+          <t>728195; 826325</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>769346; 1057510</t>
+          <t>738827; 1054383</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>951145; 1064005</t>
+          <t>957519; 1062880</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1365655; 1482575</t>
+          <t>1364502; 1482274</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1172285; 1289757</t>
+          <t>1179342; 1295341</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1435776; 2015906</t>
+          <t>1433857; 1977414</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1510894; 1648760</t>
+          <t>1508901; 1646994</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2210371; 2375709</t>
+          <t>2212676; 2370765</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1937437; 2091778</t>
+          <t>1929719; 2086393</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2299674; 3002654</t>
+          <t>2316995; 2933743</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_n_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R2-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,01; 22,22</t>
+          <t>12,65; 21,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,58; 30,12</t>
+          <t>19,47; 30,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,1; 23,33</t>
+          <t>14,29; 23,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,37; 32,34</t>
+          <t>21,97; 31,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,34; 32,57</t>
+          <t>21,18; 32,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,69; 48,06</t>
+          <t>35,32; 47,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,61; 36,57</t>
+          <t>25,38; 37,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,05; 42,37</t>
+          <t>31,47; 40,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,36; 25,69</t>
+          <t>18,38; 25,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,24; 37,16</t>
+          <t>28,57; 37,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,34; 28,33</t>
+          <t>21,57; 28,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,29; 35,32</t>
+          <t>28,47; 34,79</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,07; 17,46</t>
+          <t>10,73; 17,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,24; 30,44</t>
+          <t>21,98; 30,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,56; 27,09</t>
+          <t>19,24; 26,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,93; 30,18</t>
+          <t>21,36; 29,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,78; 34,99</t>
+          <t>26,56; 34,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,32; 46,54</t>
+          <t>37,47; 46,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,39; 41,91</t>
+          <t>33,23; 41,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,72; 42,19</t>
+          <t>34,42; 41,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,88; 25,11</t>
+          <t>19,88; 24,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,9; 37,23</t>
+          <t>30,92; 37,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,43; 33,09</t>
+          <t>27,32; 33,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,17; 34,93</t>
+          <t>29,29; 34,72</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,55; 20,7</t>
+          <t>12,35; 20,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,59; 35,12</t>
+          <t>24,95; 35,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,53; 26,39</t>
+          <t>17,97; 27,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,06; 40,14</t>
+          <t>30,58; 41,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,98; 31,35</t>
+          <t>21,95; 31,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,53; 49,52</t>
+          <t>38,4; 49,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,05; 34,11</t>
+          <t>24,14; 34,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,38; 47,81</t>
+          <t>38,99; 47,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,14; 24,46</t>
+          <t>18,19; 24,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33,28; 41,08</t>
+          <t>33,37; 40,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,41; 29,09</t>
+          <t>22,1; 29,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35,78; 42,35</t>
+          <t>36,61; 43,18</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,63; 22,6</t>
+          <t>14,48; 22,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,99; 29,62</t>
+          <t>19,96; 29,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,98; 35,31</t>
+          <t>25,44; 35,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,67; 41,18</t>
+          <t>27,01; 38,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,56; 37,43</t>
+          <t>27,75; 37,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,33; 50,2</t>
+          <t>40,31; 50,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,79; 49,23</t>
+          <t>39,18; 49,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,06; 46,78</t>
+          <t>40,75; 50,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,98; 28,21</t>
+          <t>22,25; 28,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31,91; 38,99</t>
+          <t>31,84; 38,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,52; 41,25</t>
+          <t>33,48; 40,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,05; 41,3</t>
+          <t>35,69; 43,14</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,82; 21,2</t>
+          <t>11,22; 21,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,86; 34,49</t>
+          <t>21,51; 34,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,37; 25,45</t>
+          <t>14,21; 25,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,58; 35,38</t>
+          <t>22,44; 32,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,56; 42,29</t>
+          <t>29,73; 42,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,25; 60,7</t>
+          <t>47,18; 60,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,28; 51,77</t>
+          <t>37,94; 51,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,35; 46,31</t>
+          <t>37,74; 47,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,34; 29,95</t>
+          <t>21,78; 30,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36,2; 45,55</t>
+          <t>36,04; 45,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,95; 36,85</t>
+          <t>28,43; 36,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,97; 39,27</t>
+          <t>32,3; 39,53</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,5%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,99; 22,72</t>
+          <t>14,2; 23,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,95; 38,56</t>
+          <t>27,38; 38,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,71; 26,13</t>
+          <t>16,43; 26,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32,82; 42,71</t>
+          <t>31,65; 41,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,13; 34,65</t>
+          <t>24,15; 35,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,01; 50,22</t>
+          <t>38,14; 50,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,48; 36,09</t>
+          <t>24,47; 35,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39,84; 49,92</t>
+          <t>39,41; 49,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,44; 27,38</t>
+          <t>20,05; 27,67</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34,32; 42,33</t>
+          <t>33,81; 42,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,24; 29,93</t>
+          <t>22,23; 30,06</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37,39; 44,35</t>
+          <t>37,02; 44,07</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>40,25%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,52; 20,41</t>
+          <t>14,41; 20,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,45; 27,73</t>
+          <t>21,19; 27,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,82; 24,4</t>
+          <t>17,99; 24,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,53; 39,39</t>
+          <t>31,62; 39,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,95; 31,97</t>
+          <t>24,61; 31,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,36; 41,49</t>
+          <t>34,18; 41,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,79; 33,69</t>
+          <t>26,51; 33,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43,27; 79,34</t>
+          <t>40,98; 47,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,77; 25,36</t>
+          <t>20,75; 25,41</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28,63; 33,88</t>
+          <t>28,89; 34,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,52; 28,29</t>
+          <t>23,29; 28,13</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,75; 66,31</t>
+          <t>37,5; 43,0</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,92; 23,84</t>
+          <t>17,95; 23,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,34; 24,22</t>
+          <t>17,95; 24,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,58; 27,8</t>
+          <t>21,67; 27,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,86; 24,46</t>
+          <t>19,63; 25,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,9; 33,34</t>
+          <t>27,03; 33,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,83; 34,58</t>
+          <t>27,77; 34,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,9; 38,8</t>
+          <t>31,99; 39,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,63; 38,65</t>
+          <t>31,37; 37,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23,52; 27,94</t>
+          <t>23,52; 28,08</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24,01; 28,68</t>
+          <t>24,22; 28,55</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27,72; 32,57</t>
+          <t>27,87; 32,33</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,09; 30,22</t>
+          <t>26,38; 30,71</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,14; 18,69</t>
+          <t>16,23; 18,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23,74; 26,82</t>
+          <t>23,61; 26,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21,45; 24,34</t>
+          <t>21,54; 24,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21,35; 30,48</t>
+          <t>28,07; 31,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>28,34; 31,45</t>
+          <t>28,31; 31,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,35; 41,66</t>
+          <t>38,48; 41,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,27; 36,54</t>
+          <t>33,21; 36,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>38,62; 53,27</t>
+          <t>39,05; 41,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22,67; 24,75</t>
+          <t>22,64; 24,8</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31,68; 33,94</t>
+          <t>31,65; 33,87</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27,81; 30,07</t>
+          <t>27,94; 30,08</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>32,31; 40,9</t>
+          <t>34,06; 36,27</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82468</t>
+          <t>84889</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>108718</t>
+          <t>114600</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>191186</t>
+          <t>199489</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35510; 60669</t>
+          <t>34543; 58765</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57710; 88762</t>
+          <t>57386; 89906</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41414; 68530</t>
+          <t>41986; 69226</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66570; 100729</t>
+          <t>70046; 99372</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>55656; 84958</t>
+          <t>55241; 84994</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>102530; 138057</t>
+          <t>101457; 136365</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73947; 105579</t>
+          <t>73285; 106889</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>95732; 122731</t>
+          <t>99453; 127590</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>98029; 137170</t>
+          <t>98126; 135404</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>170189; 216288</t>
+          <t>166265; 216446</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>124322; 165007</t>
+          <t>125657; 167341</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>170043; 212276</t>
+          <t>180782; 220904</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>131166</t>
+          <t>135068</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>198962</t>
+          <t>207709</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>330128</t>
+          <t>342777</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54605; 86071</t>
+          <t>52891; 85466</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>112439; 153868</t>
+          <t>111102; 152768</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98304; 136170</t>
+          <t>96678; 133525</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>108500; 156441</t>
+          <t>113323; 158552</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>134970; 176320</t>
+          <t>133870; 175217</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>195487; 243780</t>
+          <t>196262; 242820</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>174659; 219201</t>
+          <t>173807; 219387</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>178811; 217264</t>
+          <t>188076; 227023</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>198194; 250393</t>
+          <t>198227; 249071</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>318099; 383251</t>
+          <t>318210; 383698</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>281382; 339341</t>
+          <t>280219; 343492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>301473; 360958</t>
+          <t>315512; 373941</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>109560</t>
+          <t>112222</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>151412</t>
+          <t>155550</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>260972</t>
+          <t>267772</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>40008; 65998</t>
+          <t>39380; 64754</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>79695; 113806</t>
+          <t>80858; 115145</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55848; 84064</t>
+          <t>57250; 86092</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95008; 126872</t>
+          <t>96615; 130280</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>73710; 105162</t>
+          <t>73631; 106356</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>131386; 168859</t>
+          <t>130952; 168365</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80889; 114700</t>
+          <t>81183; 116749</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>137495; 166903</t>
+          <t>138939; 170917</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>118687; 160042</t>
+          <t>119016; 162680</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221309; 273219</t>
+          <t>221953; 272096</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>146744; 190489</t>
+          <t>144732; 190659</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>238012; 281711</t>
+          <t>246189; 290359</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107585</t>
+          <t>121891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>173824</t>
+          <t>190827</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>281409</t>
+          <t>312718</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52487; 81051</t>
+          <t>51921; 79888</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74759; 110778</t>
+          <t>74636; 109490</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92431; 130630</t>
+          <t>94132; 130652</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>89624; 128718</t>
+          <t>100773; 145397</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>102388; 139040</t>
+          <t>103094; 138541</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>156856; 195268</t>
+          <t>156768; 195926</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>150219; 190666</t>
+          <t>151746; 191534</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>104964; 222529</t>
+          <t>171969; 212281</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>160448; 205978</t>
+          <t>162446; 206533</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>243474; 297448</t>
+          <t>242917; 295263</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>253861; 312351</t>
+          <t>253551; 308578</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>205354; 325522</t>
+          <t>283812; 342998</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53069</t>
+          <t>56941</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>94187</t>
+          <t>97546</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>147257</t>
+          <t>154487</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22002; 43111</t>
+          <t>22814; 43206</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46484; 73341</t>
+          <t>45739; 73946</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30342; 53746</t>
+          <t>30017; 53394</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43928; 63239</t>
+          <t>46147; 67129</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>59304; 87821</t>
+          <t>61731; 88282</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>103758; 133287</t>
+          <t>103608; 132166</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83667; 113156</t>
+          <t>82937; 112640</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>50069; 119833</t>
+          <t>86386; 107956</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87707; 123098</t>
+          <t>89519; 125235</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>156469; 196858</t>
+          <t>155788; 196880</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>120138; 158384</t>
+          <t>122194; 158883</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>104873; 171795</t>
+          <t>140387; 171800</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101237</t>
+          <t>99329</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>113839</t>
+          <t>117137</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>215077</t>
+          <t>216466</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37873; 61517</t>
+          <t>38460; 63577</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73833; 105655</t>
+          <t>75018; 105815</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41345; 68746</t>
+          <t>43232; 70345</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88482; 115150</t>
+          <t>85669; 113477</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>67112; 96389</t>
+          <t>67169; 97359</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>106444; 140625</t>
+          <t>106816; 140068</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69585; 98562</t>
+          <t>66824; 97790</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>102408; 128328</t>
+          <t>103946; 129614</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>112202; 150314</t>
+          <t>110073; 151871</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>190139; 234525</t>
+          <t>187339; 233862</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>119284; 160514</t>
+          <t>119212; 161199</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>196906; 233567</t>
+          <t>197854; 235544</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>216851</t>
+          <t>258063</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>490951</t>
+          <t>342298</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>707801</t>
+          <t>600362</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>89297; 125541</t>
+          <t>88644; 126639</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>135533; 183807</t>
+          <t>140477; 184711</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>117014; 160210</t>
+          <t>118106; 162613</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>190575; 245918</t>
+          <t>227578; 286684</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>159228; 204007</t>
+          <t>157051; 204093</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>238438; 287912</t>
+          <t>237146; 289025</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>185164; 232918</t>
+          <t>183232; 234349</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>367504; 673809</t>
+          <t>316400; 368038</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>260314; 317865</t>
+          <t>260037; 318399</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>388431; 459692</t>
+          <t>391921; 461767</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>317042; 381361</t>
+          <t>313907; 379122</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>570939; 977098</t>
+          <t>559473; 641417</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>159395</t>
+          <t>178161</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>254775</t>
+          <t>285657</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>414170</t>
+          <t>463818</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>133282; 177286</t>
+          <t>133529; 177580</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>142913; 188713</t>
+          <t>139865; 188206</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>168003; 216469</t>
+          <t>168725; 217578</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>73019; 227205</t>
+          <t>156655; 202669</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>210750; 261217</t>
+          <t>211756; 263865</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>229313; 284878</t>
+          <t>228807; 283939</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>263548; 320524</t>
+          <t>264252; 322603</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>234211; 277385</t>
+          <t>260762; 309205</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>359280; 426686</t>
+          <t>359293; 428864</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>384904; 459734</t>
+          <t>388198; 457614</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>444815; 522716</t>
+          <t>447206; 518764</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>248424; 497521</t>
+          <t>429896; 500418</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>961331</t>
+          <t>1046564</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1586668</t>
+          <t>1511326</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2547999</t>
+          <t>2557890</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>528764; 612259</t>
+          <t>531817; 613638</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>813379; 919139</t>
+          <t>809215; 914675</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>728195; 826325</t>
+          <t>731051; 828740</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>738827; 1054383</t>
+          <t>991785; 1110818</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>957519; 1062880</t>
+          <t>956577; 1067183</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1364502; 1482274</t>
+          <t>1369206; 1483275</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1179342; 1295341</t>
+          <t>1177292; 1295952</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1433857; 1977414</t>
+          <t>1459245; 1566536</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1508901; 1646994</t>
+          <t>1507175; 1650446</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2212676; 2370765</t>
+          <t>2210844; 2366137</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1929719; 2086393</t>
+          <t>1938917; 2087176</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2316995; 2933743</t>
+          <t>2475849; 2636790</t>
         </is>
       </c>
     </row>
